--- a/UFC_Predictions.xlsx
+++ b/UFC_Predictions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gdsak\OneDrive\Desktop\Glicko-2, Etc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E70007F5-B568-43E1-80A6-DD901117CD58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55ECFFB5-A981-48EF-BBE8-D6386E6B30C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,6 +49,21 @@
     <t>Win %</t>
   </si>
   <si>
+    <t>Method</t>
+  </si>
+  <si>
+    <t>Method %</t>
+  </si>
+  <si>
+    <t>DEC %</t>
+  </si>
+  <si>
+    <t>(T)KO %</t>
+  </si>
+  <si>
+    <t>SUB %</t>
+  </si>
+  <si>
     <t>Value Pick</t>
   </si>
   <si>
@@ -56,21 +71,6 @@
   </si>
   <si>
     <t>Stake %</t>
-  </si>
-  <si>
-    <t>Method</t>
-  </si>
-  <si>
-    <t>Method %</t>
-  </si>
-  <si>
-    <t>DEC %</t>
-  </si>
-  <si>
-    <t>(T)KO %</t>
-  </si>
-  <si>
-    <t>SUB %</t>
   </si>
   <si>
     <t>Conor McGregor</t>
@@ -281,7 +281,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -292,6 +292,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFD3D3D3"/>
         <bgColor rgb="FFD3D3D3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -365,7 +377,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -392,6 +404,40 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -747,80 +793,80 @@
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="N1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="O1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="Q1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="O1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q1" s="6" t="s">
-        <v>11</v>
-      </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="8">
+      <c r="G2" s="17">
         <v>0.51736433403425286</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="18">
         <v>0.58891601318003006</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="3">
-        <v>0.46980364037073458</v>
-      </c>
-      <c r="L2" s="3">
-        <v>0.36650897888977357</v>
-      </c>
-      <c r="M2" s="3">
-        <v>0.46980364037073458</v>
-      </c>
-      <c r="N2" s="8">
+      <c r="K2" s="18">
+        <v>0.46980364037073469</v>
+      </c>
+      <c r="L2" s="18">
+        <v>0.36650897888977352</v>
+      </c>
+      <c r="M2" s="18">
+        <v>0.46980364037073469</v>
+      </c>
+      <c r="N2" s="17">
         <v>0.16368738073949179</v>
       </c>
-      <c r="O2" s="7" t="s">
+      <c r="O2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="P2" s="3">
-        <v>0.59348214882549888</v>
-      </c>
-      <c r="Q2" s="8">
+      <c r="P2" s="12">
+        <v>0.60683756841568459</v>
+      </c>
+      <c r="Q2" s="11">
         <v>0.05</v>
       </c>
     </row>
@@ -840,17 +886,17 @@
       <c r="E3" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="10" t="s">
         <v>23</v>
       </c>
       <c r="G3" s="8">
-        <v>0.72133371935067991</v>
+        <v>0.72133371935068002</v>
       </c>
       <c r="H3" s="7" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3">
-        <v>0.65219011733451093</v>
+        <v>0.65219011733451104</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>28</v>
@@ -867,13 +913,13 @@
       <c r="N3" s="8">
         <v>0.50540910887679102</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="O3" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="P3" s="3">
-        <v>0.20545030951892149</v>
-      </c>
-      <c r="Q3" s="8">
+      <c r="P3" s="20">
+        <v>0.28099115961153748</v>
+      </c>
+      <c r="Q3" s="21">
         <v>0.05</v>
       </c>
     </row>
@@ -893,7 +939,7 @@
       <c r="E4" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="10" t="s">
         <v>29</v>
       </c>
       <c r="G4" s="8">
@@ -918,16 +964,16 @@
         <v>0.37125984280196112</v>
       </c>
       <c r="N4" s="8">
-        <v>0.12678928719783791</v>
-      </c>
-      <c r="O4" s="7" t="s">
+        <v>0.1267892871978378</v>
+      </c>
+      <c r="O4" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="P4" s="3">
-        <v>4.8080410482940213E-2</v>
-      </c>
-      <c r="Q4" s="8">
-        <v>9.2462327851808093E-3</v>
+      <c r="P4" s="12">
+        <v>2.2788100760754881E-2</v>
+      </c>
+      <c r="Q4" s="11">
+        <v>4.3823270693759391E-3</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -946,7 +992,7 @@
       <c r="E5" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="10" t="s">
         <v>37</v>
       </c>
       <c r="G5" s="8">
@@ -962,10 +1008,10 @@
         <v>34</v>
       </c>
       <c r="K5" s="3">
-        <v>0.48230934192864711</v>
+        <v>0.482309341928647</v>
       </c>
       <c r="L5" s="3">
-        <v>0.48230934192864711</v>
+        <v>0.482309341928647</v>
       </c>
       <c r="M5" s="3">
         <v>0.34965993360279052</v>
@@ -973,119 +1019,119 @@
       <c r="N5" s="8">
         <v>0.16803072446856249</v>
       </c>
-      <c r="O5" s="7" t="s">
+      <c r="O5" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="P5" s="3">
-        <v>4.1576650488215787E-2</v>
-      </c>
-      <c r="Q5" s="8">
-        <v>2.245139126363653E-2</v>
+      <c r="P5" s="20">
+        <v>0.1060817333627349</v>
+      </c>
+      <c r="Q5" s="21">
+        <v>0.05</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="17">
         <v>0.52173926686889294</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="18">
         <v>0.53204561796555161</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="J6" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="K6" s="3">
+      <c r="K6" s="18">
         <v>0.51425399824930595</v>
       </c>
-      <c r="L6" s="3">
+      <c r="L6" s="18">
         <v>0.19185028008526531</v>
       </c>
-      <c r="M6" s="3">
+      <c r="M6" s="18">
         <v>0.29389572166542888</v>
       </c>
-      <c r="N6" s="8">
+      <c r="N6" s="17">
         <v>0.51425399824930595</v>
       </c>
-      <c r="O6" s="7" t="s">
+      <c r="O6" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="P6" s="3">
-        <v>0.21043509913583169</v>
-      </c>
-      <c r="Q6" s="8">
-        <v>3.9855132412089329E-2</v>
+      <c r="P6" s="12">
+        <v>0.22302152927409941</v>
+      </c>
+      <c r="Q6" s="11">
+        <v>4.2238925998882453E-2</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="17">
         <v>0.58121600444225952</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="I7" s="3">
+      <c r="I7" s="18">
         <v>0.53266331776016085</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="J7" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="K7" s="3">
+      <c r="K7" s="18">
         <v>0.48756662483649083</v>
       </c>
-      <c r="L7" s="3">
+      <c r="L7" s="18">
         <v>0.40591015225109511</v>
       </c>
-      <c r="M7" s="3">
+      <c r="M7" s="18">
         <v>0.48756662483649083</v>
       </c>
-      <c r="N7" s="8">
+      <c r="N7" s="17">
         <v>0.1065232229124142</v>
       </c>
-      <c r="O7" s="7" t="s">
+      <c r="O7" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="P7" s="3">
-        <v>0.5692832119941007</v>
-      </c>
-      <c r="Q7" s="8">
+      <c r="P7" s="12">
+        <v>0.62274887523059097</v>
+      </c>
+      <c r="Q7" s="11">
         <v>0.05</v>
       </c>
     </row>
@@ -1105,7 +1151,7 @@
       <c r="E8" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="10" t="s">
         <v>51</v>
       </c>
       <c r="G8" s="8">
@@ -1121,25 +1167,25 @@
         <v>22</v>
       </c>
       <c r="K8" s="3">
-        <v>0.53429134217546037</v>
+        <v>0.53429134217546026</v>
       </c>
       <c r="L8" s="3">
-        <v>0.34782970086537812</v>
+        <v>0.34782970086537818</v>
       </c>
       <c r="M8" s="3">
-        <v>0.53429134217546037</v>
+        <v>0.53429134217546026</v>
       </c>
       <c r="N8" s="8">
-        <v>0.1178789569591616</v>
-      </c>
-      <c r="O8" s="7" t="s">
+        <v>0.11787895695916149</v>
+      </c>
+      <c r="O8" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="P8" s="3">
-        <v>0.53180932235850409</v>
-      </c>
-      <c r="Q8" s="8">
-        <v>4.1418171523247983E-2</v>
+      <c r="P8" s="12">
+        <v>0.39845620583505892</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>3.103241478466191E-2</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -1158,7 +1204,7 @@
       <c r="E9" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="10" t="s">
         <v>53</v>
       </c>
       <c r="G9" s="8">
@@ -1185,11 +1231,11 @@
       <c r="N9" s="8">
         <v>0.14011793778365511</v>
       </c>
-      <c r="O9" s="7" t="s">
+      <c r="O9" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="8"/>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="11"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
@@ -1207,7 +1253,7 @@
       <c r="E10" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="10" t="s">
         <v>61</v>
       </c>
       <c r="G10" s="8">
@@ -1229,19 +1275,19 @@
         <v>0.51978869894726254</v>
       </c>
       <c r="M10" s="3">
-        <v>0.28261542570846859</v>
+        <v>0.28261542570846848</v>
       </c>
       <c r="N10" s="8">
         <v>0.1975958753442689</v>
       </c>
-      <c r="O10" s="7" t="s">
+      <c r="O10" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="P10" s="3">
-        <v>3.2117319811678868E-2</v>
-      </c>
-      <c r="Q10" s="8">
-        <v>7.4345647712219598E-3</v>
+      <c r="P10" s="12">
+        <v>3.014675590132887E-2</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>6.9784157179002011E-3</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -1260,7 +1306,7 @@
       <c r="E11" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="10" t="s">
         <v>64</v>
       </c>
       <c r="G11" s="8">
@@ -1287,13 +1333,13 @@
       <c r="N11" s="8">
         <v>0.14871560984563939</v>
       </c>
-      <c r="O11" s="7" t="s">
+      <c r="O11" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="P11" s="3">
-        <v>0.226990810438471</v>
-      </c>
-      <c r="Q11" s="8">
+      <c r="P11" s="20">
+        <v>0.30430660404980348</v>
+      </c>
+      <c r="Q11" s="21">
         <v>0.05</v>
       </c>
     </row>
@@ -1313,7 +1359,7 @@
       <c r="E12" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="10" t="s">
         <v>69</v>
       </c>
       <c r="G12" s="8">
@@ -1340,14 +1386,14 @@
       <c r="N12" s="8">
         <v>0.22161984315227409</v>
       </c>
-      <c r="O12" s="7" t="s">
+      <c r="O12" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="P12" s="3">
-        <v>0.13327484380913379</v>
-      </c>
-      <c r="Q12" s="8">
-        <v>3.0850658289151341E-2</v>
+      <c r="P12" s="20">
+        <v>0.15641774141286291</v>
+      </c>
+      <c r="Q12" s="21">
+        <v>3.6207810512236781E-2</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
@@ -1366,7 +1412,7 @@
       <c r="E13" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="10" t="s">
         <v>71</v>
       </c>
       <c r="G13" s="8">
@@ -1393,14 +1439,14 @@
       <c r="N13" s="8">
         <v>0.1235045894526464</v>
       </c>
-      <c r="O13" s="7" t="s">
+      <c r="O13" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="P13" s="3">
-        <v>4.0559218169158973E-2</v>
-      </c>
-      <c r="Q13" s="8">
-        <v>1.683207554020098E-2</v>
+      <c r="P13" s="20">
+        <v>9.5400871863962067E-2</v>
+      </c>
+      <c r="Q13" s="21">
+        <v>3.9591361823544259E-2</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
@@ -1419,11 +1465,11 @@
       <c r="E14" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="10" t="s">
         <v>77</v>
       </c>
       <c r="G14" s="8">
-        <v>0.57314199751111428</v>
+        <v>0.57314199751111439</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>77</v>
@@ -1446,14 +1492,14 @@
       <c r="N14" s="8">
         <v>0.14855654345132749</v>
       </c>
-      <c r="O14" s="7" t="s">
+      <c r="O14" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="P14" s="3">
-        <v>0.29764832756621251</v>
-      </c>
-      <c r="Q14" s="8">
-        <v>3.6476510731153503E-2</v>
+      <c r="P14" s="12">
+        <v>0.24317501183496071</v>
+      </c>
+      <c r="Q14" s="11">
+        <v>2.9800859293500091E-2</v>
       </c>
     </row>
   </sheetData>
